--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2021_los_lagos.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2021_los_lagos.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 20:08</t>
+    <t xml:space="preserve">2026-08-02 19:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2021_los_lagos.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2021_los_lagos.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-02 19:52</t>
+    <t xml:space="preserve">2026-08-05 10:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2021_los_lagos.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2021_los_lagos.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:48</t>
+    <t xml:space="preserve">2026-08-16 09:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2021_los_lagos.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2021_los_lagos.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 09:57</t>
+    <t xml:space="preserve">2026-08-19 12:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2021_los_lagos.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2021_los_lagos.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 12:52</t>
+    <t xml:space="preserve">2026-08-28 11:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2021_los_lagos.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2021_los_lagos.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:48</t>
+    <t xml:space="preserve">2026-09-06 17:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
